--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945237F4-B7DC-436F-8CC4-2A1F3B9E2AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F73C7DC-94EC-46E1-ABE1-45E9E07E440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,12 @@
   </si>
   <si>
     <t>Had a nice conversation with my classmate.</t>
+  </si>
+  <si>
+    <t>not satisfied</t>
+  </si>
+  <si>
+    <t>my CA doesn’t go well not satisfied with  the presentation I gave.</t>
   </si>
 </sst>
 </file>
@@ -1547,27 +1553,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B17" s="14">
+        <v>350</v>
+      </c>
+      <c r="C17" s="14">
+        <v>160</v>
+      </c>
+      <c r="D17" s="14">
+        <v>50</v>
+      </c>
+      <c r="E17" s="14">
+        <v>20</v>
+      </c>
+      <c r="F17" s="14">
+        <v>350</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>150</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F73C7DC-94EC-46E1-ABE1-45E9E07E440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0464324B-5AC6-4795-BBF6-8AA63D0092B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>my CA doesn’t go well not satisfied with  the presentation I gave.</t>
+  </si>
+  <si>
+    <t>I realised something about me today</t>
   </si>
 </sst>
 </file>
@@ -1599,27 +1602,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B18" s="14">
+        <v>400</v>
+      </c>
+      <c r="C18" s="14">
+        <v>160</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>350</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>160</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0464324B-5AC6-4795-BBF6-8AA63D0092B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55912101-5A57-4402-9F2F-CCD9C955FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>I realised something about me today</t>
+  </si>
+  <si>
+    <t>Tired</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>Learn new things.</t>
   </si>
 </sst>
 </file>
@@ -1649,26 +1658,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B19" s="14">
+        <v>400</v>
+      </c>
+      <c r="C19" s="14">
+        <v>200</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>200</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55912101-5A57-4402-9F2F-CCD9C955FCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71382E85-993D-40D3-B1BD-45479FF21AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Learn new things.</t>
+  </si>
+  <si>
+    <t>no holiday on weekend.</t>
   </si>
 </sst>
 </file>
@@ -1704,26 +1707,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>100</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>20</v>
+      </c>
+      <c r="F20" s="14">
+        <v>50</v>
+      </c>
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14">
+        <v>500</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71382E85-993D-40D3-B1BD-45479FF21AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDC1317-519B-465B-A8AE-207B699ED2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t>no holiday on weekend.</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>preparing for ca</t>
   </si>
 </sst>
 </file>
@@ -1753,26 +1762,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>50</v>
+      </c>
+      <c r="D21" s="14">
+        <v>300</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>300</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDC1317-519B-465B-A8AE-207B699ED2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1F4EF4-83F5-4A13-9E5C-023D52B875D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>preparing for ca</t>
+  </si>
+  <si>
+    <t>Ca went good</t>
   </si>
 </sst>
 </file>
@@ -1808,26 +1811,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B22" s="14">
+        <v>350</v>
+      </c>
+      <c r="C22" s="14">
+        <v>100</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>150</v>
+      </c>
+      <c r="G22" s="14">
+        <v>30</v>
+      </c>
+      <c r="H22" s="14">
+        <v>250</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1F4EF4-83F5-4A13-9E5C-023D52B875D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A5E584-90FD-4F25-B54C-3FA64356FA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Ca went good</t>
+  </si>
+  <si>
+    <t>a peacefull day</t>
   </si>
 </sst>
 </file>
@@ -1857,26 +1860,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>150</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>200</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A5E584-90FD-4F25-B54C-3FA64356FA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22193A1E-81FE-4E0B-8078-DE83A12B5C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>a peacefull day</t>
+  </si>
+  <si>
+    <t>learn new things.</t>
   </si>
 </sst>
 </file>
@@ -1906,26 +1909,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>100</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>400</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22193A1E-81FE-4E0B-8078-DE83A12B5C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7F995D-97CA-4DCE-BC29-4818390702EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>learn new things.</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>not well today</t>
   </si>
 </sst>
 </file>
@@ -1955,26 +1961,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>120</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>45</v>
+      </c>
+      <c r="F25" s="14">
+        <v>100</v>
+      </c>
+      <c r="G25" s="14">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12629342 (1).xlsx
+++ b/12629342 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bhumika\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7F995D-97CA-4DCE-BC29-4818390702EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19904E6-5E78-4584-85C2-19632C8453B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>not well today</t>
+  </si>
+  <si>
+    <t>completed pending work</t>
   </si>
 </sst>
 </file>
@@ -2007,48 +2010,94 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>200</v>
+      </c>
+      <c r="D26" s="14">
+        <v>50</v>
+      </c>
+      <c r="E26" s="14">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>100</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B27" s="14">
+        <v>300</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>200</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
